--- a/Meggi/provider_cost_inputs.xlsx
+++ b/Meggi/provider_cost_inputs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qmao\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/Meggi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC7222F3-2870-4DA9-B4DC-C8D2AFA30A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{AC7222F3-2870-4DA9-B4DC-C8D2AFA30A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8D5698C-82F5-4EAD-ACBA-E81EB0193400}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="732" yWindow="732" windowWidth="11556" windowHeight="6144" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1014,15 +1014,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C198"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="53.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" style="6" customWidth="1"/>
-    <col min="3" max="3" width="13.875" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1033,7 +1034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -1044,7 +1045,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -1055,7 +1056,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
@@ -1066,7 +1067,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1075,7 +1076,7 @@
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1084,7 +1085,7 @@
       </c>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1093,7 +1094,7 @@
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,7 +1103,7 @@
       </c>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1111,7 +1112,7 @@
       </c>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -1122,7 +1123,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>12</v>
       </c>
@@ -1133,7 +1134,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -1142,7 +1143,7 @@
       </c>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1153,7 +1154,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -1162,7 +1163,7 @@
       </c>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1173,7 +1174,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -1182,7 +1183,7 @@
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>18</v>
       </c>
@@ -1193,7 +1194,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -1202,7 +1203,7 @@
       </c>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>20</v>
       </c>
@@ -1213,7 +1214,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -1222,7 +1223,7 @@
       </c>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -1233,7 +1234,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -1242,7 +1243,7 @@
       </c>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -1251,7 +1252,7 @@
       </c>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -1262,7 +1263,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -1273,7 +1274,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -1282,7 +1283,7 @@
       </c>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -1293,7 +1294,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -1302,7 +1303,7 @@
       </c>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -1311,7 +1312,7 @@
       </c>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
@@ -1322,7 +1323,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -1333,7 +1334,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
@@ -1342,7 +1343,7 @@
       </c>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
@@ -1353,7 +1354,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>35</v>
       </c>
@@ -1362,7 +1363,7 @@
       </c>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>36</v>
       </c>
@@ -1371,7 +1372,7 @@
       </c>
       <c r="C35" s="1"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>37</v>
       </c>
@@ -1380,7 +1381,7 @@
       </c>
       <c r="C36" s="1"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -1389,7 +1390,7 @@
       </c>
       <c r="C37" s="1"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
@@ -1398,7 +1399,7 @@
       </c>
       <c r="C38" s="1"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>40</v>
       </c>
@@ -1407,7 +1408,7 @@
       </c>
       <c r="C39" s="1"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>41</v>
       </c>
@@ -1418,7 +1419,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
@@ -1427,7 +1428,7 @@
       </c>
       <c r="C41" s="1"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>43</v>
       </c>
@@ -1436,7 +1437,7 @@
       </c>
       <c r="C42" s="1"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>44</v>
       </c>
@@ -1445,7 +1446,7 @@
       </c>
       <c r="C43" s="1"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>45</v>
       </c>
@@ -1454,7 +1455,7 @@
       </c>
       <c r="C44" s="1"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>46</v>
       </c>
@@ -1463,7 +1464,7 @@
       </c>
       <c r="C45" s="1"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>47</v>
       </c>
@@ -1472,7 +1473,7 @@
       </c>
       <c r="C46" s="1"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>48</v>
       </c>
@@ -1481,7 +1482,7 @@
       </c>
       <c r="C47" s="1"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>49</v>
       </c>
@@ -1490,7 +1491,7 @@
       </c>
       <c r="C48" s="1"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>50</v>
       </c>
@@ -1499,7 +1500,7 @@
       </c>
       <c r="C49" s="1"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>51</v>
       </c>
@@ -1508,7 +1509,7 @@
       </c>
       <c r="C50" s="1"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>52</v>
       </c>
@@ -1517,7 +1518,7 @@
       </c>
       <c r="C51" s="1"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>53</v>
       </c>
@@ -1526,7 +1527,7 @@
       </c>
       <c r="C52" s="1"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>54</v>
       </c>
@@ -1535,7 +1536,7 @@
       </c>
       <c r="C53" s="1"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>55</v>
       </c>
@@ -1546,7 +1547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>56</v>
       </c>
@@ -1557,7 +1558,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>57</v>
       </c>
@@ -1566,7 +1567,7 @@
       </c>
       <c r="C56" s="1"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>58</v>
       </c>
@@ -1577,7 +1578,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>59</v>
       </c>
@@ -1586,7 +1587,7 @@
       </c>
       <c r="C58" s="1"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>60</v>
       </c>
@@ -1595,7 +1596,7 @@
       </c>
       <c r="C59" s="1"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>61</v>
       </c>
@@ -1604,7 +1605,7 @@
       </c>
       <c r="C60" s="1"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>62</v>
       </c>
@@ -1613,7 +1614,7 @@
       </c>
       <c r="C61" s="1"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>63</v>
       </c>
@@ -1622,7 +1623,7 @@
       </c>
       <c r="C62" s="1"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>64</v>
       </c>
@@ -1631,7 +1632,7 @@
       </c>
       <c r="C63" s="1"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>65</v>
       </c>
@@ -1642,7 +1643,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>66</v>
       </c>
@@ -1653,7 +1654,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>67</v>
       </c>
@@ -1662,7 +1663,7 @@
       </c>
       <c r="C66" s="1"/>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>68</v>
       </c>
@@ -1671,7 +1672,7 @@
       </c>
       <c r="C67" s="1"/>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>69</v>
       </c>
@@ -1680,7 +1681,7 @@
       </c>
       <c r="C68" s="1"/>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>70</v>
       </c>
@@ -1691,7 +1692,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>71</v>
       </c>
@@ -1702,7 +1703,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>72</v>
       </c>
@@ -1713,7 +1714,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>73</v>
       </c>
@@ -1722,7 +1723,7 @@
       </c>
       <c r="C72" s="1"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>74</v>
       </c>
@@ -1731,7 +1732,7 @@
       </c>
       <c r="C73" s="1"/>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>75</v>
       </c>
@@ -1740,7 +1741,7 @@
       </c>
       <c r="C74" s="1"/>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>76</v>
       </c>
@@ -1749,7 +1750,7 @@
       </c>
       <c r="C75" s="1"/>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>77</v>
       </c>
@@ -1758,7 +1759,7 @@
       </c>
       <c r="C76" s="1"/>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>78</v>
       </c>
@@ -1767,7 +1768,7 @@
       </c>
       <c r="C77" s="1"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>79</v>
       </c>
@@ -1776,7 +1777,7 @@
       </c>
       <c r="C78" s="1"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>80</v>
       </c>
@@ -1785,7 +1786,7 @@
       </c>
       <c r="C79" s="1"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>81</v>
       </c>
@@ -1794,7 +1795,7 @@
       </c>
       <c r="C80" s="1"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>82</v>
       </c>
@@ -1803,7 +1804,7 @@
       </c>
       <c r="C81" s="1"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>83</v>
       </c>
@@ -1812,7 +1813,7 @@
       </c>
       <c r="C82" s="1"/>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>84</v>
       </c>
@@ -1821,7 +1822,7 @@
       </c>
       <c r="C83" s="1"/>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>85</v>
       </c>
@@ -1830,7 +1831,7 @@
       </c>
       <c r="C84" s="1"/>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>86</v>
       </c>
@@ -1841,7 +1842,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>87</v>
       </c>
@@ -1850,7 +1851,7 @@
       </c>
       <c r="C86" s="1"/>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>88</v>
       </c>
@@ -1859,7 +1860,7 @@
       </c>
       <c r="C87" s="1"/>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>89</v>
       </c>
@@ -1870,7 +1871,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>90</v>
       </c>
@@ -1879,7 +1880,7 @@
       </c>
       <c r="C89" s="1"/>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>91</v>
       </c>
@@ -1888,7 +1889,7 @@
       </c>
       <c r="C90" s="1"/>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>92</v>
       </c>
@@ -1897,7 +1898,7 @@
       </c>
       <c r="C91" s="1"/>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>93</v>
       </c>
@@ -1906,7 +1907,7 @@
       </c>
       <c r="C92" s="1"/>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>94</v>
       </c>
@@ -1917,7 +1918,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>95</v>
       </c>
@@ -1926,7 +1927,7 @@
       </c>
       <c r="C94" s="1"/>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>96</v>
       </c>
@@ -1937,7 +1938,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>97</v>
       </c>
@@ -1946,7 +1947,7 @@
       </c>
       <c r="C96" s="1"/>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>98</v>
       </c>
@@ -1955,7 +1956,7 @@
       </c>
       <c r="C97" s="1"/>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>99</v>
       </c>
@@ -1964,7 +1965,7 @@
       </c>
       <c r="C98" s="1"/>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>100</v>
       </c>
@@ -1973,7 +1974,7 @@
       </c>
       <c r="C99" s="1"/>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>101</v>
       </c>
@@ -1982,7 +1983,7 @@
       </c>
       <c r="C100" s="1"/>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>102</v>
       </c>
@@ -1991,7 +1992,7 @@
       </c>
       <c r="C101" s="1"/>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>103</v>
       </c>
@@ -2002,7 +2003,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>104</v>
       </c>
@@ -2011,7 +2012,7 @@
       </c>
       <c r="C103" s="1"/>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>105</v>
       </c>
@@ -2020,7 +2021,7 @@
       </c>
       <c r="C104" s="1"/>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>106</v>
       </c>
@@ -2029,7 +2030,7 @@
       </c>
       <c r="C105" s="1"/>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>107</v>
       </c>
@@ -2038,7 +2039,7 @@
       </c>
       <c r="C106" s="1"/>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>108</v>
       </c>
@@ -2047,7 +2048,7 @@
       </c>
       <c r="C107" s="1"/>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>109</v>
       </c>
@@ -2056,7 +2057,7 @@
       </c>
       <c r="C108" s="1"/>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>110</v>
       </c>
@@ -2067,7 +2068,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>111</v>
       </c>
@@ -2076,7 +2077,7 @@
       </c>
       <c r="C110" s="1"/>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>112</v>
       </c>
@@ -2085,7 +2086,7 @@
       </c>
       <c r="C111" s="1"/>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>113</v>
       </c>
@@ -2094,7 +2095,7 @@
       </c>
       <c r="C112" s="1"/>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>114</v>
       </c>
@@ -2103,7 +2104,7 @@
       </c>
       <c r="C113" s="1"/>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>115</v>
       </c>
@@ -2112,7 +2113,7 @@
       </c>
       <c r="C114" s="1"/>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>116</v>
       </c>
@@ -2121,7 +2122,7 @@
       </c>
       <c r="C115" s="1"/>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>117</v>
       </c>
@@ -2130,7 +2131,7 @@
       </c>
       <c r="C116" s="1"/>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>118</v>
       </c>
@@ -2141,7 +2142,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>119</v>
       </c>
@@ -2150,7 +2151,7 @@
       </c>
       <c r="C118" s="1"/>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>120</v>
       </c>
@@ -2161,7 +2162,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>121</v>
       </c>
@@ -2172,7 +2173,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>122</v>
       </c>
@@ -2181,7 +2182,7 @@
       </c>
       <c r="C121" s="1"/>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>123</v>
       </c>
@@ -2190,7 +2191,7 @@
       </c>
       <c r="C122" s="1"/>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>124</v>
       </c>
@@ -2199,7 +2200,7 @@
       </c>
       <c r="C123" s="1"/>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>125</v>
       </c>
@@ -2208,7 +2209,7 @@
       </c>
       <c r="C124" s="1"/>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>126</v>
       </c>
@@ -2217,7 +2218,7 @@
       </c>
       <c r="C125" s="1"/>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>127</v>
       </c>
@@ -2228,7 +2229,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>128</v>
       </c>
@@ -2239,7 +2240,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>129</v>
       </c>
@@ -2250,7 +2251,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>130</v>
       </c>
@@ -2259,7 +2260,7 @@
       </c>
       <c r="C129" s="1"/>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>131</v>
       </c>
@@ -2268,7 +2269,7 @@
       </c>
       <c r="C130" s="1"/>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>132</v>
       </c>
@@ -2277,7 +2278,7 @@
       </c>
       <c r="C131" s="1"/>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>133</v>
       </c>
@@ -2286,7 +2287,7 @@
       </c>
       <c r="C132" s="1"/>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>134</v>
       </c>
@@ -2295,7 +2296,7 @@
       </c>
       <c r="C133" s="1"/>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>135</v>
       </c>
@@ -2304,7 +2305,7 @@
       </c>
       <c r="C134" s="1"/>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>136</v>
       </c>
@@ -2313,7 +2314,7 @@
       </c>
       <c r="C135" s="1"/>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>137</v>
       </c>
@@ -2322,7 +2323,7 @@
       </c>
       <c r="C136" s="1"/>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>138</v>
       </c>
@@ -2333,7 +2334,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>139</v>
       </c>
@@ -2342,7 +2343,7 @@
       </c>
       <c r="C138" s="1"/>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>140</v>
       </c>
@@ -2351,7 +2352,7 @@
       </c>
       <c r="C139" s="1"/>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>141</v>
       </c>
@@ -2360,7 +2361,7 @@
       </c>
       <c r="C140" s="1"/>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>142</v>
       </c>
@@ -2369,7 +2370,7 @@
       </c>
       <c r="C141" s="1"/>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>143</v>
       </c>
@@ -2378,7 +2379,7 @@
       </c>
       <c r="C142" s="1"/>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>144</v>
       </c>
@@ -2387,7 +2388,7 @@
       </c>
       <c r="C143" s="1"/>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>145</v>
       </c>
@@ -2396,7 +2397,7 @@
       </c>
       <c r="C144" s="1"/>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>146</v>
       </c>
@@ -2405,7 +2406,7 @@
       </c>
       <c r="C145" s="1"/>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>147</v>
       </c>
@@ -2416,7 +2417,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>148</v>
       </c>
@@ -2425,7 +2426,7 @@
       </c>
       <c r="C147" s="1"/>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>149</v>
       </c>
@@ -2434,7 +2435,7 @@
       </c>
       <c r="C148" s="1"/>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>150</v>
       </c>
@@ -2443,7 +2444,7 @@
       </c>
       <c r="C149" s="1"/>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>151</v>
       </c>
@@ -2452,7 +2453,7 @@
       </c>
       <c r="C150" s="1"/>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>152</v>
       </c>
@@ -2461,7 +2462,7 @@
       </c>
       <c r="C151" s="1"/>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>153</v>
       </c>
@@ -2470,7 +2471,7 @@
       </c>
       <c r="C152" s="1"/>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>154</v>
       </c>
@@ -2479,7 +2480,7 @@
       </c>
       <c r="C153" s="1"/>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>155</v>
       </c>
@@ -2490,7 +2491,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>156</v>
       </c>
@@ -2501,7 +2502,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>157</v>
       </c>
@@ -2510,7 +2511,7 @@
       </c>
       <c r="C156" s="1"/>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>158</v>
       </c>
@@ -2519,7 +2520,7 @@
       </c>
       <c r="C157" s="1"/>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>159</v>
       </c>
@@ -2528,7 +2529,7 @@
       </c>
       <c r="C158" s="1"/>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>160</v>
       </c>
@@ -2537,7 +2538,7 @@
       </c>
       <c r="C159" s="1"/>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>161</v>
       </c>
@@ -2546,7 +2547,7 @@
       </c>
       <c r="C160" s="1"/>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>162</v>
       </c>
@@ -2555,7 +2556,7 @@
       </c>
       <c r="C161" s="1"/>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>163</v>
       </c>
@@ -2564,7 +2565,7 @@
       </c>
       <c r="C162" s="1"/>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>164</v>
       </c>
@@ -2573,7 +2574,7 @@
       </c>
       <c r="C163" s="1"/>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>165</v>
       </c>
@@ -2582,7 +2583,7 @@
       </c>
       <c r="C164" s="1"/>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>166</v>
       </c>
@@ -2591,7 +2592,7 @@
       </c>
       <c r="C165" s="1"/>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>167</v>
       </c>
@@ -2600,7 +2601,7 @@
       </c>
       <c r="C166" s="1"/>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>168</v>
       </c>
@@ -2609,7 +2610,7 @@
       </c>
       <c r="C167" s="1"/>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>169</v>
       </c>
@@ -2618,7 +2619,7 @@
       </c>
       <c r="C168" s="1"/>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>170</v>
       </c>
@@ -2629,7 +2630,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>171</v>
       </c>
@@ -2638,7 +2639,7 @@
       </c>
       <c r="C170" s="1"/>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>172</v>
       </c>
@@ -2647,7 +2648,7 @@
       </c>
       <c r="C171" s="1"/>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>173</v>
       </c>
@@ -2656,7 +2657,7 @@
       </c>
       <c r="C172" s="1"/>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>174</v>
       </c>
@@ -2665,7 +2666,7 @@
       </c>
       <c r="C173" s="1"/>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>175</v>
       </c>
@@ -2674,7 +2675,7 @@
       </c>
       <c r="C174" s="1"/>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>176</v>
       </c>
@@ -2683,7 +2684,7 @@
       </c>
       <c r="C175" s="1"/>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>177</v>
       </c>
@@ -2692,7 +2693,7 @@
       </c>
       <c r="C176" s="1"/>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>178</v>
       </c>
@@ -2701,7 +2702,7 @@
       </c>
       <c r="C177" s="1"/>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>179</v>
       </c>
@@ -2710,7 +2711,7 @@
       </c>
       <c r="C178" s="1"/>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>180</v>
       </c>
@@ -2719,7 +2720,7 @@
       </c>
       <c r="C179" s="1"/>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>181</v>
       </c>
@@ -2728,7 +2729,7 @@
       </c>
       <c r="C180" s="1"/>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>182</v>
       </c>
@@ -2737,7 +2738,7 @@
       </c>
       <c r="C181" s="1"/>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>183</v>
       </c>
@@ -2746,7 +2747,7 @@
       </c>
       <c r="C182" s="1"/>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>184</v>
       </c>
@@ -2755,7 +2756,7 @@
       </c>
       <c r="C183" s="1"/>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>185</v>
       </c>
@@ -2764,7 +2765,7 @@
       </c>
       <c r="C184" s="1"/>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>186</v>
       </c>
@@ -2773,7 +2774,7 @@
       </c>
       <c r="C185" s="1"/>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>187</v>
       </c>
@@ -2782,7 +2783,7 @@
       </c>
       <c r="C186" s="1"/>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>188</v>
       </c>
@@ -2791,7 +2792,7 @@
       </c>
       <c r="C187" s="1"/>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>189</v>
       </c>
@@ -2800,7 +2801,7 @@
       </c>
       <c r="C188" s="1"/>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>190</v>
       </c>
@@ -2809,7 +2810,7 @@
       </c>
       <c r="C189" s="1"/>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>191</v>
       </c>
@@ -2818,7 +2819,7 @@
       </c>
       <c r="C190" s="1"/>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>192</v>
       </c>
@@ -2827,7 +2828,7 @@
       </c>
       <c r="C191" s="1"/>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>193</v>
       </c>
@@ -2838,7 +2839,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>194</v>
       </c>
@@ -2847,7 +2848,7 @@
       </c>
       <c r="C193" s="1"/>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>195</v>
       </c>
@@ -2856,7 +2857,7 @@
       </c>
       <c r="C194" s="1"/>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>196</v>
       </c>
@@ -2865,7 +2866,7 @@
       </c>
       <c r="C195" s="1"/>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>197</v>
       </c>
@@ -2874,7 +2875,7 @@
       </c>
       <c r="C196" s="1"/>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>198</v>
       </c>
@@ -2883,7 +2884,7 @@
       </c>
       <c r="C197" s="1"/>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>199</v>
       </c>
@@ -2893,6 +2894,13 @@
       <c r="C198" s="1"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C198" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
